--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -474,20 +474,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -496,20 +490,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -518,20 +506,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -540,20 +522,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -562,20 +538,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,20 +554,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -606,20 +570,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -628,20 +586,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -650,20 +602,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -672,18 +618,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-0.023587</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -692,20 +634,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -714,20 +650,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -736,20 +666,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.275024</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.265057</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.40696</v>
       </c>
     </row>
     <row r="17">
@@ -758,20 +682,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -824,20 +742,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.275024</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.265057</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.40696</v>
       </c>
     </row>
     <row r="21">
@@ -846,20 +758,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -868,20 +774,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -922,20 +822,14 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -966,20 +860,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.275024</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.265057</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.40696</v>
       </c>
     </row>
     <row r="28">
@@ -988,20 +876,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.000398</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.000391</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.00034</v>
       </c>
     </row>
     <row r="29">
@@ -1010,20 +892,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.274626</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.264666</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.40662</v>
       </c>
     </row>
     <row r="30">
@@ -1054,20 +930,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1105,20 +975,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1127,20 +991,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1149,20 +1007,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1171,20 +1023,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1193,20 +1039,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1215,20 +1055,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1237,20 +1071,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1275,20 +1103,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1297,20 +1119,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1319,20 +1135,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1341,20 +1151,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1363,20 +1167,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1385,20 +1183,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1407,20 +1199,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.236588</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.241585</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.172658</v>
       </c>
     </row>
     <row r="49">
@@ -1445,20 +1231,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1467,20 +1247,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1489,20 +1263,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1511,20 +1279,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1533,20 +1295,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1577,20 +1333,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1599,20 +1349,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1621,20 +1365,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>3.823891</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3.326581</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>3.531581</v>
       </c>
     </row>
     <row r="59">
@@ -1643,20 +1381,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1665,20 +1397,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1687,20 +1413,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.017805</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.025787</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.009291000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -1709,20 +1429,14 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>3.841696</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>3.352368</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>3.540872</v>
       </c>
     </row>
     <row r="63">
@@ -1763,20 +1477,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1785,20 +1493,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1807,20 +1509,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1829,20 +1525,14 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.465621</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.242808</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.131398</v>
       </c>
     </row>
     <row r="69">
@@ -1851,20 +1541,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.523587</v>
       </c>
     </row>
     <row r="70">
@@ -1873,20 +1557,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1895,20 +1573,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.523587</v>
       </c>
     </row>
     <row r="72">
@@ -1917,20 +1589,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1939,20 +1605,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1961,20 +1621,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1983,20 +1637,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2023,20 +1671,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2045,20 +1687,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2067,20 +1703,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2099,10 +1729,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.1285276322859806</v>
       </c>
     </row>
     <row r="81">
@@ -2111,20 +1739,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2133,20 +1755,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2155,20 +1771,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2177,20 +1787,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2199,20 +1803,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2226,15 +1824,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -2243,20 +1837,14 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.465621</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0.242808</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.654985</v>
       </c>
     </row>
     <row r="88">
@@ -2265,20 +1853,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>7.410527</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>7.413162</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>7.415797</v>
       </c>
     </row>
     <row r="89">
@@ -2287,20 +1869,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2325,20 +1901,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2363,20 +1933,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2401,20 +1965,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2423,20 +1981,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>3.62955</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>3.371177</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>4.073731</v>
       </c>
     </row>
     <row r="97">
@@ -2468,20 +2020,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.275024</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.265057</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.40696</v>
       </c>
     </row>
     <row r="100">
@@ -2490,20 +2036,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2512,20 +2052,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.004599</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0.004355</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>-0.003787</v>
       </c>
     </row>
     <row r="102">
@@ -2534,20 +2068,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2556,20 +2084,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.013957</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0.004421</v>
       </c>
     </row>
     <row r="104">
@@ -2578,20 +2100,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.278089</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.216027</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>-0.150874</v>
       </c>
     </row>
     <row r="105">
@@ -2600,20 +2116,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2622,20 +2132,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.27394</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.225629</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.15024</v>
       </c>
     </row>
     <row r="107">
@@ -2644,20 +2148,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.291914</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.006749</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.004579</v>
       </c>
     </row>
     <row r="108">
@@ -2666,20 +2164,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2688,20 +2180,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2710,20 +2196,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2732,20 +2212,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2754,20 +2228,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2776,20 +2244,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2798,20 +2260,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2820,20 +2276,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2842,20 +2292,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2864,20 +2308,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2886,20 +2324,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.025931</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0.008633</v>
       </c>
     </row>
     <row r="119">
@@ -2908,20 +2340,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0.197358</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.44872</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-0.14938</v>
       </c>
     </row>
     <row r="120">
@@ -2930,20 +2356,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2952,20 +2372,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2974,20 +2388,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2996,20 +2404,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3018,20 +2420,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3040,20 +2436,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3062,20 +2452,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3106,20 +2490,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.024642</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-6.499999999999999e-05</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>-6.499999999999999e-05</v>
       </c>
     </row>
     <row r="129">
@@ -3160,20 +2538,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3182,20 +2554,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.215984</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.008959999999999999</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.935494</v>
       </c>
     </row>
     <row r="133">
@@ -3220,20 +2586,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3242,20 +2602,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.708772</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.457615</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.520061</v>
       </c>
     </row>
   </sheetData>
@@ -3536,7 +2890,11 @@
           <t>Exploration and evaluation assets 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>3.823891</v>
       </c>
@@ -3627,7 +2985,11 @@
           <t>Loan payable 9, 20</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4034,7 +3396,11 @@
           <t>Loss for the year $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-1.275024</v>
       </c>
@@ -4061,7 +3427,11 @@
           <t>Loss on the sale of exploration and evaluation assets 6</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -4121,7 +3491,11 @@
           <t>Share-based payments 11</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -4181,7 +3555,11 @@
           <t>Gain on derecognition of trade payables 8</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4212,7 +3590,11 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.004599</v>
       </c>
@@ -4239,7 +3621,11 @@
           <t>Prepaids</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
         <v>0.00045</v>
       </c>
@@ -4266,7 +3652,11 @@
           <t>Trade and other payables 8</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.278089</v>
       </c>
@@ -4442,7 +3832,11 @@
           <t>Cash (used in) provided by investing activities</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -4533,7 +3927,11 @@
           <t>Share issue costs 10</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4713,7 +4111,11 @@
           <t>Loss on the sale of exploration and evaluation assets</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -4744,7 +4146,11 @@
           <t>Share-based payments 10</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>0.291914</v>
       </c>
@@ -4862,7 +4268,11 @@
           <t>Share issue costs 9</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
         <v>-0.024642</v>
       </c>
@@ -5189,7 +4599,11 @@
           <t>Other income</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -5220,11 +4634,7 @@
           <t>Finance costs 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>InterestExpenseNonOperating</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.001746</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.001355</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>0</v>
+        <v>0.001015</v>
       </c>
     </row>
     <row r="54">
@@ -2629,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2813,7 +2813,11 @@
           <t>Equipment 5</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.001746</v>
       </c>
@@ -3772,12 +3776,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of exploration and evaluation</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of exploration and evaluation expenditures</t>
+          <t>Proceeds from the sale of exploration and evaluation 6expenditures</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -3803,7 +3807,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of exploration and evaluation</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3830,7 +3834,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of exploration and evaluation</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4082,7 +4086,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2. BASIS OF PREPARATION AND GOING CONCERN</t>
+          <t>2.  BASIS OF PREPARATION AND GOING CONCERN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4107,28 +4111,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Loss on the sale of exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>For the Years Ended February 28, 2025 and February</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.025931</v>
+        <v>2.9e-05</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -4149,19 +4143,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Share-based payments 10</t>
+          <t>Loss on the sale of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0.291914</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.006749</v>
+        <v>0.025931</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -4177,20 +4173,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prepaid exploration expenditure</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Share-based payments 10</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
-        <v>0.026327</v>
+        <v>0.291914</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-0.008373</v>
+        <v>0.006749</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -4206,20 +4206,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Proceeds from the sale of exploration and evaluation</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash provided in investing activities</t>
+          <t>Prepaid exploration expenditure</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>0.197358</v>
+        <v>0.026327</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.44872</v>
+        <v>-0.008373</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -4235,22 +4235,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Private placement</t>
+          <t>Proceeds from the sale of exploration and evaluation                                                   6 expenditures</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>0.75204</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.5675</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -4266,24 +4266,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Share issue costs 9</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Cash provided in investing activities</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" s="5" t="n">
-        <v>-0.024642</v>
+        <v>0.197358</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>0.44872</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4304,19 +4300,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Net cash (used) provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Private placement</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.727398</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>-6.499999999999999e-05</v>
+        <v>0.75204</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4337,15 +4331,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(Decrease) increase in cash during the year</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Share issue costs 9</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
-        <v>0.215984</v>
+        <v>-0.024642</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.008959999999999999</v>
+        <v>-6.499999999999999e-05</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -4356,119 +4354,121 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Administrative and general 12,13 $</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash (used) provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.727398</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.227379</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>0.349894</v>
+        <v>-6.499999999999999e-05</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Corporate development</t>
+          <t>(Decrease) increase in cash during the year</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" s="5" t="n">
-        <v>0.1055</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.215984</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-0.008959999999999999</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Supplemental cash flow information – Note 15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wages &amp; benefits 12,13</t>
+          <t>FOR THE YEARS ENDED FEBRUARY 28, 2025 AND FEBRUARY</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.138165</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.017977</v>
+        <v>2.9e-05</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>purchase warrants.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Depreciation 5</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>FOR THE YEARS ENDED FEBRUARY 28, 2025 AND FEBRUARY</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" s="5" t="n">
-        <v>0.000398</v>
+        <v>0.002024</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.000391</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.00034</v>
+        <v>2.9e-05</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -4484,18 +4484,20 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Administrative and general 12,13 $</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.02955</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.057774</v>
+        <v>0.227379</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.044911</v>
+        <v>0.349894</v>
       </c>
     </row>
     <row r="61">
@@ -4511,20 +4513,20 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Share-based payments 11,13</t>
+          <t>Corporate development</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0.006749</v>
+      <c r="E61" s="5" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.004579</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="62">
@@ -4540,22 +4542,20 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>TotalExpenses</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-1.279266</v>
+          <t>Wages &amp; benefits 12,13</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.31491</v>
+        <v>0.138165</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.427201</v>
+        <v>0.017977</v>
       </c>
     </row>
     <row r="63">
@@ -4566,27 +4566,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Other income and expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Depreciation 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.004242</v>
+        <v>0.000398</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.005784</v>
+        <v>0.000391</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.002719</v>
+        <v>0.00034</v>
       </c>
     </row>
     <row r="64">
@@ -4597,31 +4597,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Other income and expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.02955</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057774</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.044911</v>
       </c>
     </row>
     <row r="65">
@@ -4632,12 +4628,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other income and expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Finance costs 9</t>
+          <t>Share-based payments 11,13</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -4646,13 +4642,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.006749</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>-0.023587</v>
+        <v>0.004579</v>
       </c>
     </row>
     <row r="66">
@@ -4663,27 +4657,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other income and expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Gain on derecognition of trade payables 8</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>TotalExpenses</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>-1.279266</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-0.31491</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.049742</v>
+        <v>-0.427201</v>
       </c>
     </row>
     <row r="67">
@@ -4699,20 +4693,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Loss on sale of exploration and evaluation asset 6</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0.004242</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.025931</v>
+        <v>0.005784</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>-0.008633</v>
+        <v>0.002719</v>
       </c>
     </row>
     <row r="68">
@@ -4728,22 +4724,26 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>-1.275024</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.265057</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.40696</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4759,24 +4759,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Loss per share for the period basic and diluted 14 $</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Finance costs 9</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>0</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0</v>
+        <v>-0.023587</v>
       </c>
     </row>
     <row r="70">
@@ -4787,25 +4785,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income and expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Administrative and general 11,12 $</t>
+          <t>Gain on derecognition of trade payables 8</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.246014</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>0.227379</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.049742</v>
       </c>
     </row>
     <row r="71">
@@ -4816,25 +4816,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income and expenses</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Wages &amp; benefits 12</t>
+          <t>Loss on sale of exploration and evaluation asset 6</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.238503</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.138165</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.025931</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-0.008633</v>
       </c>
     </row>
     <row r="72">
@@ -4845,27 +4845,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income and expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Property evaluation</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
-        <v>0.471387</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.275024</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.265057</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>-0.40696</v>
       </c>
     </row>
     <row r="73">
@@ -4876,25 +4876,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other income and expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share-based payments 12</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>0.187914</v>
+          <t>Loss per share for the period basic and diluted 14 $</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.006749</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4903,24 +4907,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Other income and expenses</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Loss on sale of exploration and evaluation assets</t>
+          <t>For the Years Ended February 28, 2025 and February</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E74" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-0.025931</v>
+        <v>2.9e-05</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4936,26 +4934,175 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Administrative and general 11,12 $</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>0.246014</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0.227379</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Wages &amp; benefits 12</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>0.238503</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.138165</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Property evaluation</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>0.471387</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Share-based payments 12</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.187914</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0.006749</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>Other income and expenses</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Loss on sale of exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>-0.025931</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other income and expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
         <is>
           <t>Loss per share for the period basic and diluted 13 $</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E80" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="F80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>0.171031</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.025931</v>
+        <v>-0.084476</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.008633</v>
+        <v>-0.156903</v>
       </c>
     </row>
     <row r="119">
@@ -2873,7 +2873,11 @@
           <t>Prepaids and deposits 6</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.008559000000000001</v>
       </c>
@@ -3815,7 +3819,11 @@
           <t>Exploration and evaluation asset expenditures 6</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>0.171031</v>
       </c>

--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1.279266</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.31491</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.427201</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-1.279266</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-0.31491</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.427201</v>
       </c>
     </row>
     <row r="12">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004242</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005784</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002719</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.275024</v>
+        <v>-1.279266</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.265057</v>
+        <v>-0.270841</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.40696</v>
+        <v>-0.409679</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.274626</v>
+        <v>-1.278868</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.264666</v>
+        <v>-0.27045</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.40662</v>
+        <v>-0.409339</v>
       </c>
     </row>
     <row r="30">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.234618</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.225658</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.161152</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.234618</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.225658</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.161152</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.236588</v>
+        <v>0.00197</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.241585</v>
+        <v>0.015927</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.172658</v>
+        <v>0.011506</v>
       </c>
     </row>
     <row r="49">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4675,17 +4675,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>-1.279266</v>
+        <v>1.279266</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>-0.31491</v>
+        <v>0.31491</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>-0.427201</v>
+        <v>0.427201</v>
       </c>
     </row>
     <row r="67">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">

--- a/output/pdf_financials_xlsx/SAO.xlsx
+++ b/output/pdf_financials_xlsx/SAO.xlsx
@@ -4311,7 +4311,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>0.75204</v>
       </c>
